--- a/data_extactor/batch_10_fa/trimmed/batch_0091_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0091_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | استدلال قیاسی | درک کتبی | دقت در کنترل ابزار | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | بینایی نزدیک | استدلال قیاسی | درک کتبی | دقت کنترل | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | تکنسین‌های علوم زیست‌محیطی و بهداشت محیط | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای نیروگاه برق | سرویس‌کاران سپتیک‌تانک و لایروب‌های خطوط فاضلاب | مهندسان آب و فاضلاب</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های علوم و بهداشت محیط زیست | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای نیروگاه برق | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | یادگیری فعال | درک مطلب | سخن گفتن | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فراوری | شیمی | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | دید نزدیک | استدلال قیاسی | درک شفاهی | دقت در کنترل ابزار | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | توجه انتخابی | بینایی نزدیک | استدلال قیاسی | درک شفاهی | دقت کنترل | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | تکنسین‌های شیمی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
+          <t>مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تکنسین‌های شیمی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | تولید و فراوری</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>سرعت ادراک | دید نزدیک | حساسیت به مسئله | توجه انتخابی | درک شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>سرعت ادراکی | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی | درک شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | نصابان و تعمیرکاران شیرآلات و ادوات کنترلی به استثنای درب‌های اتوماتیک | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | مهندسان مکانیک تأسیسات و اپراتورهای بویلر</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فراوری | ایمنی و امنیت عمومی | مکانیک | مدیریت و امور اداری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | ایمنی و امنیت عمومی | مکانیک | مدیریت و اداره | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | سرعت ادراک | دید نزدیک | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | دقت در کنترل ابزار</t>
+          <t>ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | دقت کنترل</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مهندسان نفت | اپراتورهای پمپ به استثنای سرچاهی | اپراتورهای خدمات چاه‌های نفت و گاز | اپراتورهای پمپاژ سرچاهی</t>
+          <t>اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مهندسان نفت | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | اپراتورهای واحدهای خدمات چاه نفت و گاز | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | فیزیک | شیمی | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | تولید و فرآوری | فیزیک | شیمی | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای نیروگاه برق | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | مکانیک‌های ماشین‌آلات صنعتی</t>
+          <t>اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | مکانیک‌های ماشین‌آلات صنعتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی</t>
+          <t>درک مطلب | نظارت | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت در کنترل ابزار | درک شفاهی | درک کتبی | توجه انتخابی | سرعت ادراک | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>دقت کنترل | درک شفاهی | درک کتبی | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
+          <t>مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فراوری | شیمی | مکانیک | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دقت در کنترل ابزار | دید نزدیک | درک کتبی | سرعت ادراک | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | دقت کنترل | بینایی نزدیک | درک کتبی | سرعت ادراکی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | تکنسین‌های شیمی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اختلاط و ترکیب مواد | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
+          <t>مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های شیمی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | سرعت ادراک | حساسیت به مسئله | ثبات دست و بازو | مرتب‌سازی اطلاعات | هماهنگی چند اندام | دقت در کنترل ابزار</t>
+          <t>بینایی نزدیک | سرعت ادراکی | حساسیت به مسئله | ثبات دست و بازو | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | دقت کنترل</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌شکنی، آسیاب و پرداخت | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | کارگران تغذیه و تخلیه ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اختلاط و ترکیب مواد | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار SAP | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فراوری | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت در کنترل ابزار | زمان واکنش | کنترل نرخ حرکت | هماهنگی چند اندام | ثبات دست و بازو | دید نزدیک</t>
+          <t>مهارت دستی | دقت کنترل | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | ثبات دست و بازو | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلزات و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران تغذیه و تخلیه ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اختلاط و ترکیب مواد</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دقت در کنترل ابزار | دید نزدیک | چابکی دستی | هماهنگی چند اندام | توجه انتخابی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | دقت کنترل | بینایی نزدیک | مهارت دستی | هماهنگی چند عضو | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | کارگران تغذیه و تخلیه ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلزات و پلاستیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
